--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -926,6 +926,126 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127921333</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100053</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Igelkott</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Erinaceus europaeus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rosenhällsvägen, 371 52 Karlskrona, Bl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>541522</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6232137</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Augerum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Möller</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>WWF - Tillsammans för Sveriges igelkottar</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>127921333</v>
       </c>
       <c r="B4" t="n">
-        <v>56585</v>
+        <v>56612</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>127921333</v>
       </c>
       <c r="B4" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>127921333</v>
       </c>
       <c r="B4" t="n">
-        <v>56615</v>
+        <v>56618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -931,7 +931,7 @@
         <v>127921333</v>
       </c>
       <c r="B4" t="n">
-        <v>56618</v>
+        <v>56620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,60 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96574680</v>
+        <v>87265884</v>
       </c>
       <c r="B2" t="n">
-        <v>76570</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4196</v>
+        <v>406</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig jordtunga</t>
+          <t>Nötkörvel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Geoglossum fallax</t>
+          <t>Conopodium majus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E.J.Durand</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
+          <t>(Gouan) Loret</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bastasjö ängar Norra delen, Karlskrona, Bl</t>
+          <t>Bastasjö, Bl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541474.6095906775</v>
+        <v>541482</v>
       </c>
       <c r="R2" t="n">
-        <v>6232317.646215202</v>
+        <v>6232158</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2008-07-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,27 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Niclas Wahlgren</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>101934282</v>
+        <v>96574680</v>
       </c>
       <c r="B3" t="n">
-        <v>9302</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,53 +783,44 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>101246</v>
+        <v>4196</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ekoxe</t>
+          <t>Fjällig jordtunga</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lucanus cervus</t>
+          <t>Geoglossum fallax</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>E.J.Durand</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bastasjövägen 84, Karlskrona, Bl</t>
+          <t>Bastasjö ängar Norra delen, Karlskrona, Bl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541402.2462160975</v>
+        <v>541475</v>
       </c>
       <c r="R3" t="n">
-        <v>6232199.12340346</v>
+        <v>6232318</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,22 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-06-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>18:36</t>
+          <t>2021-10-10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Therese Ahlman</t>
+          <t>Niclas Wahlgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Therese Ahlman</t>
+          <t>Niclas Wahlgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -931,11 +882,11 @@
         <v>127921333</v>
       </c>
       <c r="B4" t="n">
-        <v>56620</v>
+        <v>56845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1037,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Möller</t>
+          <t>Via Johan Möller</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1045,6 +996,132 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>101934282</v>
+      </c>
+      <c r="B5" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bastasjövägen 84, Karlskrona, Bl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>541402</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6232199</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Karlskrona</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Blekinge</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Augerum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-06-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Ahlman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Ahlman</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42540-2025 artfynd.xlsx
+++ b/artfynd/A 42540-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87265884</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96574680</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>WWF - Tillsammans för Sveriges igelkottar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127921333</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1122,8 +1142,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101934282</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>